--- a/Uno_API/Uno_API/wwwroot/templates/ExcelSample1_TourRooming_Import.xlsx
+++ b/Uno_API/Uno_API/wwwroot/templates/ExcelSample1_TourRooming_Import.xlsx
@@ -6,6 +6,7 @@
     <sheet name="Tours" sheetId="1" r:id="rId1"/>
     <sheet name="Projects" sheetId="2" r:id="rId2"/>
     <sheet name="Rooming" sheetId="3" r:id="rId3"/>
+    <sheet name="Hotels" sheetId="4" r:id="rId4"/>
   </sheets>
 </workbook>
 </file>
@@ -435,7 +436,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>BVP01092026</v>
+        <v>BVP05072026</v>
       </c>
       <c r="B2" t="str">
         <v>PRJ-BVP1</v>
@@ -444,10 +445,10 @@
         <v>Budapest-Vienna-Prague</v>
       </c>
       <c r="D2" t="str">
-        <v>01.09.2026</v>
+        <v>05.07.2026</v>
       </c>
       <c r="E2" t="str">
-        <v>07.09.2026</v>
+        <v>12.07.2026</v>
       </c>
       <c r="F2">
         <v>27</v>
@@ -504,13 +505,13 @@
         <v>Apex Travel Agency</v>
       </c>
       <c r="C2" t="str">
-        <v>Orta Avrupa 2026 Autumn Tours</v>
+        <v>Orta Avrupa 2026 Summer Tours</v>
       </c>
       <c r="D2" t="str">
-        <v>01.09.2026</v>
+        <v>01.07.2026</v>
       </c>
       <c r="E2" t="str">
-        <v>30.09.2026</v>
+        <v>31.07.2026</v>
       </c>
       <c r="F2" t="str">
         <v>EUR</v>
@@ -564,7 +565,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>BKG-01-BVP01092026</v>
+        <v>BKG-01-BVP05072026</v>
       </c>
       <c r="B2" t="str">
         <v>Ahmet</v>
@@ -599,7 +600,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>BKG-01-BVP01092026</v>
+        <v>BKG-01-BVP05072026</v>
       </c>
       <c r="B3" t="str">
         <v>Ayşe</v>
@@ -634,7 +635,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>BKG-02-BVP01092026</v>
+        <v>BKG-02-BVP05072026</v>
       </c>
       <c r="B4" t="str">
         <v>Mehmet</v>
@@ -669,7 +670,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>BKG-02-BVP01092026</v>
+        <v>BKG-02-BVP05072026</v>
       </c>
       <c r="B5" t="str">
         <v>Fatma</v>
@@ -704,7 +705,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>BKG-02-BVP01092026</v>
+        <v>BKG-02-BVP05072026</v>
       </c>
       <c r="B6" t="str">
         <v>Can</v>
@@ -742,4 +743,215 @@
     <ignoredError numberStoredAsText="1" sqref="A1:K6"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:P4"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Hotel Name</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Location</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Star Rating</v>
+      </c>
+      <c r="D1" t="str">
+        <v>Pricing Basis (Pax/Room)</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Single Room Rate (€)</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Single Pax Rate (€)</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Double Room Rate (€)</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Double Pax Rate (€)</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Twin Room Rate (€)</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Twin Pax Rate (€)</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Triple Room Rate (€)</v>
+      </c>
+      <c r="L1" t="str">
+        <v>Triple Pax Rate (€)</v>
+      </c>
+      <c r="M1" t="str">
+        <v>Contact Name</v>
+      </c>
+      <c r="N1" t="str">
+        <v>Contact Role</v>
+      </c>
+      <c r="O1" t="str">
+        <v>Email</v>
+      </c>
+      <c r="P1" t="str">
+        <v>Phone</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>Hotel Canada</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Budapest</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Pax</v>
+      </c>
+      <c r="E2">
+        <v>62</v>
+      </c>
+      <c r="F2">
+        <v>62</v>
+      </c>
+      <c r="G2">
+        <v>92</v>
+      </c>
+      <c r="H2">
+        <v>46</v>
+      </c>
+      <c r="I2">
+        <v>92</v>
+      </c>
+      <c r="J2">
+        <v>46</v>
+      </c>
+      <c r="K2">
+        <v>120</v>
+      </c>
+      <c r="L2">
+        <v>40</v>
+      </c>
+      <c r="M2" t="str">
+        <v>János Kovács</v>
+      </c>
+      <c r="N2" t="str">
+        <v>Reservation Manager</v>
+      </c>
+      <c r="O2" t="str">
+        <v>janos@hotelcanada.hu</v>
+      </c>
+      <c r="P2" t="str">
+        <v>+36 1 234 5678</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>Hotel Allegro</v>
+      </c>
+      <c r="B3" t="str">
+        <v>Vienna</v>
+      </c>
+      <c r="C3">
+        <v>4</v>
+      </c>
+      <c r="D3" t="str">
+        <v>Pax</v>
+      </c>
+      <c r="E3">
+        <v>77</v>
+      </c>
+      <c r="F3">
+        <v>77</v>
+      </c>
+      <c r="G3">
+        <v>84</v>
+      </c>
+      <c r="H3">
+        <v>42</v>
+      </c>
+      <c r="I3">
+        <v>84</v>
+      </c>
+      <c r="J3">
+        <v>42</v>
+      </c>
+      <c r="K3">
+        <v>111</v>
+      </c>
+      <c r="L3">
+        <v>37</v>
+      </c>
+      <c r="M3" t="str">
+        <v>Markus Weber</v>
+      </c>
+      <c r="N3" t="str">
+        <v>Front Desk</v>
+      </c>
+      <c r="O3" t="str">
+        <v>m.weber@allegro-vienna.at</v>
+      </c>
+      <c r="P3" t="str">
+        <v>+43 1 987 6543</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>Hotel Olympik</v>
+      </c>
+      <c r="B4" t="str">
+        <v>Prague</v>
+      </c>
+      <c r="C4">
+        <v>4</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Room</v>
+      </c>
+      <c r="E4">
+        <v>72</v>
+      </c>
+      <c r="F4">
+        <v>72</v>
+      </c>
+      <c r="G4">
+        <v>80</v>
+      </c>
+      <c r="H4">
+        <v>40</v>
+      </c>
+      <c r="I4">
+        <v>80</v>
+      </c>
+      <c r="J4">
+        <v>40</v>
+      </c>
+      <c r="K4">
+        <v>108</v>
+      </c>
+      <c r="L4">
+        <v>36</v>
+      </c>
+      <c r="M4" t="str">
+        <v>Eva Dvořáková</v>
+      </c>
+      <c r="N4" t="str">
+        <v>Sales Director</v>
+      </c>
+      <c r="O4" t="str">
+        <v>eva@olympik.cz</v>
+      </c>
+      <c r="P4" t="str">
+        <v>+420 283 001 111</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:P4"/>
+  </ignoredErrors>
+</worksheet>
 </file>